--- a/Scout/waukee-vs-valley-091826.xlsx
+++ b/Scout/waukee-vs-valley-091826.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R8341d7fc6aa94073"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R17fb248e9fe74672"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -106,6 +118,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -142,6 +157,9 @@
     <t>MESH</t>
   </si>
   <si>
+    <t>K</t>
+  </si>
+  <si>
     <t>L</t>
   </si>
   <si>
@@ -166,9 +184,6 @@
     <t>TOWARD</t>
   </si>
   <si>
-    <t>K</t>
-  </si>
-  <si>
     <t>Extra Pt.</t>
   </si>
   <si>
@@ -184,6 +199,9 @@
     <t>D</t>
   </si>
   <si>
+    <t>GUN</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
@@ -202,6 +220,9 @@
     <t>Y OFF TRIPS PRO</t>
   </si>
   <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
     <t>CLOSED WING</t>
   </si>
   <si>
@@ -223,6 +244,12 @@
     <t>Punt</t>
   </si>
   <si>
+    <t>G GUN</t>
+  </si>
+  <si>
+    <t>K GUN</t>
+  </si>
+  <si>
     <t>Y OFF TRIPS</t>
   </si>
   <si>
@@ -247,6 +274,9 @@
     <t>SLANT</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>PRO WING</t>
   </si>
   <si>
@@ -259,6 +289,9 @@
     <t>Y SCREEN</t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>Y OFF EMPTY</t>
   </si>
   <si>
@@ -277,6 +310,9 @@
     <t>POWER</t>
   </si>
   <si>
+    <t>GUN STACK K</t>
+  </si>
+  <si>
     <t>TWINS OPEN</t>
   </si>
   <si>
@@ -290,6 +326,9 @@
   </si>
   <si>
     <t>EMPTY</t>
+  </si>
+  <si>
+    <t>G I DOT UNDER</t>
   </si>
   <si>
     <t>CLOSED</t>
@@ -314,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y110"/>
+  <dimension ref="A1:AC110"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -392,6 +431,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -401,7 +452,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -412,7 +463,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -424,33 +475,36 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J3">
         <v>45</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T3" t="s">
-        <v>33</v>
-      </c>
-      <c r="U3" t="s">
-        <v>31</v>
-      </c>
-      <c r="X3">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -462,7 +516,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -474,33 +528,36 @@
         <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" t="s">
         <v>35</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U4" t="s">
-        <v>31</v>
-      </c>
-      <c r="X4">
+      <c r="W4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -512,7 +569,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -524,27 +581,30 @@
         <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J5">
         <v>-5</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R5" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" t="s">
-        <v>31</v>
-      </c>
-      <c r="X5">
+        <v>41</v>
+      </c>
+      <c r="P5" t="s">
+        <v>35</v>
+      </c>
+      <c r="W5" t="s">
+        <v>36</v>
+      </c>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -556,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -568,36 +628,39 @@
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" t="s">
-        <v>31</v>
-      </c>
-      <c r="S6" t="s">
-        <v>40</v>
-      </c>
-      <c r="T6" t="s">
-        <v>42</v>
-      </c>
-      <c r="U6" t="s">
-        <v>31</v>
-      </c>
-      <c r="V6" t="s">
-        <v>31</v>
-      </c>
-      <c r="X6">
+        <v>41</v>
+      </c>
+      <c r="P6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W6" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -609,7 +672,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -621,33 +684,36 @@
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J7">
         <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R7" t="s">
-        <v>43</v>
-      </c>
-      <c r="S7" t="s">
-        <v>44</v>
-      </c>
-      <c r="T7" t="s">
-        <v>45</v>
-      </c>
-      <c r="U7" t="s">
-        <v>31</v>
-      </c>
-      <c r="X7">
+        <v>34</v>
+      </c>
+      <c r="P7" t="s">
+        <v>48</v>
+      </c>
+      <c r="W7" t="s">
+        <v>49</v>
+      </c>
+      <c r="X7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -659,7 +725,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -671,33 +737,36 @@
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" t="s">
-        <v>43</v>
-      </c>
-      <c r="S8" t="s">
-        <v>46</v>
-      </c>
-      <c r="T8" t="s">
-        <v>47</v>
-      </c>
-      <c r="U8" t="s">
-        <v>31</v>
-      </c>
-      <c r="X8">
+        <v>41</v>
+      </c>
+      <c r="P8" t="s">
+        <v>48</v>
+      </c>
+      <c r="W8" t="s">
+        <v>49</v>
+      </c>
+      <c r="X8" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -709,7 +778,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -721,33 +790,36 @@
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J9">
         <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>30</v>
-      </c>
-      <c r="R9" t="s">
-        <v>43</v>
-      </c>
-      <c r="S9" t="s">
-        <v>49</v>
-      </c>
-      <c r="T9" t="s">
-        <v>50</v>
-      </c>
-      <c r="U9" t="s">
-        <v>43</v>
-      </c>
-      <c r="X9">
+        <v>34</v>
+      </c>
+      <c r="P9" t="s">
+        <v>48</v>
+      </c>
+      <c r="W9" t="s">
+        <v>49</v>
+      </c>
+      <c r="X9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -759,21 +831,21 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I10" t="s">
-        <v>53</v>
-      </c>
-      <c r="X10">
+        <v>58</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -785,19 +857,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F11">
         <v>-40</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -808,7 +880,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -820,33 +892,36 @@
         <v>-44</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J12">
         <v>14</v>
       </c>
       <c r="K12" t="s">
-        <v>36</v>
-      </c>
-      <c r="R12" t="s">
-        <v>57</v>
-      </c>
-      <c r="S12" t="s">
-        <v>58</v>
-      </c>
-      <c r="U12" t="s">
-        <v>43</v>
-      </c>
-      <c r="V12" t="s">
-        <v>43</v>
-      </c>
-      <c r="X12">
+        <v>41</v>
+      </c>
+      <c r="P12" t="s">
+        <v>62</v>
+      </c>
+      <c r="W12" t="s">
+        <v>63</v>
+      </c>
+      <c r="X12" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -858,7 +933,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -870,21 +945,21 @@
         <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
-      </c>
-      <c r="V13" t="s">
-        <v>31</v>
-      </c>
-      <c r="X13">
+        <v>34</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -896,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -908,33 +983,36 @@
         <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J14">
         <v>-5</v>
       </c>
       <c r="K14" t="s">
-        <v>30</v>
-      </c>
-      <c r="R14" t="s">
-        <v>31</v>
-      </c>
-      <c r="S14" t="s">
-        <v>40</v>
-      </c>
-      <c r="U14" t="s">
-        <v>31</v>
-      </c>
-      <c r="V14" t="s">
-        <v>43</v>
-      </c>
-      <c r="X14">
+        <v>34</v>
+      </c>
+      <c r="P14" t="s">
+        <v>48</v>
+      </c>
+      <c r="W14" t="s">
+        <v>36</v>
+      </c>
+      <c r="X14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -946,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -958,30 +1036,33 @@
         <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J15">
         <v>40</v>
       </c>
       <c r="K15" t="s">
-        <v>36</v>
-      </c>
-      <c r="R15" t="s">
-        <v>31</v>
-      </c>
-      <c r="S15" t="s">
-        <v>60</v>
-      </c>
-      <c r="U15" t="s">
-        <v>31</v>
-      </c>
-      <c r="X15">
+        <v>41</v>
+      </c>
+      <c r="P15" t="s">
+        <v>48</v>
+      </c>
+      <c r="W15" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -993,7 +1074,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1005,30 +1086,33 @@
         <v>7</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J16">
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>36</v>
-      </c>
-      <c r="R16" t="s">
-        <v>43</v>
-      </c>
-      <c r="S16" t="s">
-        <v>61</v>
-      </c>
-      <c r="U16" t="s">
-        <v>31</v>
-      </c>
-      <c r="X16">
+        <v>41</v>
+      </c>
+      <c r="P16" t="s">
+        <v>48</v>
+      </c>
+      <c r="W16" t="s">
+        <v>49</v>
+      </c>
+      <c r="X16" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -1040,7 +1124,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1052,30 +1136,33 @@
         <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I17" t="s">
+        <v>40</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>41</v>
+      </c>
+      <c r="P17" t="s">
         <v>35</v>
       </c>
-      <c r="J17">
-        <v>2</v>
-      </c>
-      <c r="K17" t="s">
-        <v>36</v>
-      </c>
-      <c r="R17" t="s">
-        <v>43</v>
-      </c>
-      <c r="S17" t="s">
-        <v>62</v>
-      </c>
-      <c r="U17" t="s">
-        <v>31</v>
-      </c>
-      <c r="X17">
+      <c r="W17" t="s">
+        <v>49</v>
+      </c>
+      <c r="X17" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -1087,7 +1174,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1099,33 +1186,36 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>36</v>
-      </c>
-      <c r="R18" t="s">
-        <v>43</v>
-      </c>
-      <c r="S18" t="s">
-        <v>63</v>
-      </c>
-      <c r="U18" t="s">
-        <v>43</v>
-      </c>
-      <c r="V18" t="s">
-        <v>43</v>
-      </c>
-      <c r="X18">
+        <v>41</v>
+      </c>
+      <c r="P18" t="s">
+        <v>69</v>
+      </c>
+      <c r="W18" t="s">
+        <v>49</v>
+      </c>
+      <c r="X18" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB18">
         <v>1</v>
       </c>
     </row>
@@ -1137,21 +1227,21 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F19">
         <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
-      </c>
-      <c r="X19">
+        <v>58</v>
+      </c>
+      <c r="AB19">
         <v>1</v>
       </c>
     </row>
@@ -1163,19 +1253,19 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F20">
         <v>-40</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H20" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I20" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
@@ -1186,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1198,33 +1288,36 @@
         <v>-20</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J21">
         <v>9</v>
       </c>
       <c r="K21" t="s">
-        <v>30</v>
-      </c>
-      <c r="R21" t="s">
-        <v>31</v>
-      </c>
-      <c r="S21" t="s">
-        <v>44</v>
-      </c>
-      <c r="T21" t="s">
-        <v>66</v>
-      </c>
-      <c r="U21" t="s">
-        <v>31</v>
-      </c>
-      <c r="X21">
+        <v>34</v>
+      </c>
+      <c r="P21" t="s">
+        <v>48</v>
+      </c>
+      <c r="W21" t="s">
+        <v>36</v>
+      </c>
+      <c r="X21" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1236,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -1248,36 +1341,39 @@
         <v>-29</v>
       </c>
       <c r="G22" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I22" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>36</v>
-      </c>
-      <c r="R22" t="s">
-        <v>43</v>
-      </c>
-      <c r="S22" t="s">
-        <v>40</v>
-      </c>
-      <c r="T22" t="s">
-        <v>67</v>
-      </c>
-      <c r="U22" t="s">
-        <v>31</v>
-      </c>
-      <c r="V22" t="s">
-        <v>31</v>
-      </c>
-      <c r="X22">
+        <v>41</v>
+      </c>
+      <c r="P22" t="s">
+        <v>48</v>
+      </c>
+      <c r="W22" t="s">
+        <v>49</v>
+      </c>
+      <c r="X22" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1289,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -1301,33 +1397,36 @@
         <v>-29</v>
       </c>
       <c r="G23" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I23" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>36</v>
-      </c>
-      <c r="R23" t="s">
-        <v>31</v>
-      </c>
-      <c r="S23" t="s">
-        <v>32</v>
-      </c>
-      <c r="T23" t="s">
-        <v>68</v>
-      </c>
-      <c r="U23" t="s">
-        <v>31</v>
-      </c>
-      <c r="X23">
+        <v>41</v>
+      </c>
+      <c r="P23" t="s">
+        <v>48</v>
+      </c>
+      <c r="W23" t="s">
+        <v>36</v>
+      </c>
+      <c r="X23" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1339,7 +1438,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -1351,15 +1450,15 @@
         <v>-29</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I24" t="s">
-        <v>55</v>
-      </c>
-      <c r="X24">
+        <v>60</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1371,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1383,30 +1482,33 @@
         <v>-28</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I25" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>30</v>
-      </c>
-      <c r="R25" t="s">
-        <v>31</v>
-      </c>
-      <c r="S25" t="s">
-        <v>40</v>
-      </c>
-      <c r="U25" t="s">
-        <v>31</v>
-      </c>
-      <c r="X25">
+        <v>34</v>
+      </c>
+      <c r="P25" t="s">
+        <v>77</v>
+      </c>
+      <c r="W25" t="s">
+        <v>36</v>
+      </c>
+      <c r="X25" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1418,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -1430,33 +1532,36 @@
         <v>-28</v>
       </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H26" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J26">
         <v>5</v>
       </c>
       <c r="K26" t="s">
-        <v>36</v>
-      </c>
-      <c r="R26" t="s">
-        <v>43</v>
-      </c>
-      <c r="S26" t="s">
-        <v>40</v>
-      </c>
-      <c r="U26" t="s">
-        <v>31</v>
-      </c>
-      <c r="V26" t="s">
-        <v>31</v>
-      </c>
-      <c r="X26">
+        <v>41</v>
+      </c>
+      <c r="P26" t="s">
+        <v>48</v>
+      </c>
+      <c r="W26" t="s">
+        <v>49</v>
+      </c>
+      <c r="X26" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1468,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -1480,33 +1585,36 @@
         <v>-33</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J27">
         <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>30</v>
-      </c>
-      <c r="R27" t="s">
-        <v>43</v>
-      </c>
-      <c r="S27" t="s">
-        <v>40</v>
-      </c>
-      <c r="U27" t="s">
-        <v>31</v>
-      </c>
-      <c r="V27" t="s">
-        <v>43</v>
-      </c>
-      <c r="X27">
+        <v>34</v>
+      </c>
+      <c r="P27" t="s">
+        <v>78</v>
+      </c>
+      <c r="W27" t="s">
+        <v>49</v>
+      </c>
+      <c r="X27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1518,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -1530,33 +1638,36 @@
         <v>-37</v>
       </c>
       <c r="G28" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J28">
         <v>4</v>
       </c>
       <c r="K28" t="s">
-        <v>36</v>
-      </c>
-      <c r="R28" t="s">
-        <v>31</v>
-      </c>
-      <c r="S28" t="s">
-        <v>63</v>
-      </c>
-      <c r="U28" t="s">
-        <v>31</v>
-      </c>
-      <c r="V28" t="s">
-        <v>31</v>
-      </c>
-      <c r="X28">
+        <v>41</v>
+      </c>
+      <c r="P28" t="s">
+        <v>69</v>
+      </c>
+      <c r="W28" t="s">
+        <v>36</v>
+      </c>
+      <c r="X28" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1568,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1580,33 +1691,36 @@
         <v>-41</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H29" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I29" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>30</v>
-      </c>
-      <c r="R29" t="s">
-        <v>31</v>
-      </c>
-      <c r="S29" t="s">
-        <v>40</v>
-      </c>
-      <c r="U29" t="s">
-        <v>43</v>
-      </c>
-      <c r="V29" t="s">
-        <v>43</v>
-      </c>
-      <c r="X29">
+        <v>34</v>
+      </c>
+      <c r="P29" t="s">
+        <v>48</v>
+      </c>
+      <c r="W29" t="s">
+        <v>36</v>
+      </c>
+      <c r="X29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1618,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -1630,30 +1744,33 @@
         <v>-41</v>
       </c>
       <c r="G30" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H30" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I30" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J30">
         <v>8</v>
       </c>
       <c r="K30" t="s">
-        <v>36</v>
-      </c>
-      <c r="R30" t="s">
-        <v>43</v>
-      </c>
-      <c r="S30" t="s">
-        <v>70</v>
-      </c>
-      <c r="U30" t="s">
-        <v>31</v>
-      </c>
-      <c r="X30">
+        <v>41</v>
+      </c>
+      <c r="P30" t="s">
+        <v>35</v>
+      </c>
+      <c r="W30" t="s">
+        <v>49</v>
+      </c>
+      <c r="X30" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1665,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -1677,30 +1794,33 @@
         <v>-49</v>
       </c>
       <c r="G31" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" t="s">
+        <v>80</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31" t="s">
         <v>34</v>
       </c>
-      <c r="I31" t="s">
-        <v>71</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31" t="s">
-        <v>30</v>
-      </c>
-      <c r="R31" t="s">
-        <v>43</v>
-      </c>
-      <c r="S31" t="s">
-        <v>72</v>
-      </c>
-      <c r="U31" t="s">
-        <v>43</v>
-      </c>
-      <c r="X31">
+      <c r="P31" t="s">
+        <v>48</v>
+      </c>
+      <c r="W31" t="s">
+        <v>49</v>
+      </c>
+      <c r="X31" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB31">
         <v>2</v>
       </c>
     </row>
@@ -1712,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1724,33 +1844,36 @@
         <v>50</v>
       </c>
       <c r="G32" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H32" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>36</v>
-      </c>
-      <c r="R32" t="s">
-        <v>31</v>
-      </c>
-      <c r="S32" t="s">
-        <v>49</v>
-      </c>
-      <c r="T32" t="s">
-        <v>73</v>
-      </c>
-      <c r="U32" t="s">
-        <v>43</v>
-      </c>
-      <c r="X32">
+        <v>41</v>
+      </c>
+      <c r="P32" t="s">
+        <v>48</v>
+      </c>
+      <c r="W32" t="s">
+        <v>36</v>
+      </c>
+      <c r="X32" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB32">
         <v>3</v>
       </c>
     </row>
@@ -1762,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1774,33 +1897,36 @@
         <v>50</v>
       </c>
       <c r="G33" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H33" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I33" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>36</v>
-      </c>
-      <c r="R33" t="s">
-        <v>31</v>
-      </c>
-      <c r="S33" t="s">
-        <v>46</v>
-      </c>
-      <c r="T33" t="s">
-        <v>45</v>
-      </c>
-      <c r="U33" t="s">
-        <v>31</v>
-      </c>
-      <c r="X33">
+        <v>41</v>
+      </c>
+      <c r="P33" t="s">
+        <v>35</v>
+      </c>
+      <c r="W33" t="s">
+        <v>36</v>
+      </c>
+      <c r="X33" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB33">
         <v>3</v>
       </c>
     </row>
@@ -1812,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -1824,33 +1950,36 @@
         <v>50</v>
       </c>
       <c r="G34" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H34" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I34" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J34">
         <v>37</v>
       </c>
       <c r="K34" t="s">
-        <v>30</v>
-      </c>
-      <c r="R34" t="s">
-        <v>31</v>
-      </c>
-      <c r="S34" t="s">
-        <v>32</v>
-      </c>
-      <c r="T34" t="s">
-        <v>74</v>
-      </c>
-      <c r="U34" t="s">
-        <v>31</v>
-      </c>
-      <c r="X34">
+        <v>34</v>
+      </c>
+      <c r="P34" t="s">
+        <v>35</v>
+      </c>
+      <c r="W34" t="s">
+        <v>36</v>
+      </c>
+      <c r="X34" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB34">
         <v>3</v>
       </c>
     </row>
@@ -1862,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1874,18 +2003,18 @@
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I35" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>36</v>
-      </c>
-      <c r="X35">
+        <v>41</v>
+      </c>
+      <c r="AB35">
         <v>3</v>
       </c>
     </row>
@@ -1897,7 +2026,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1909,33 +2038,36 @@
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H36" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I36" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J36">
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>30</v>
-      </c>
-      <c r="R36" t="s">
-        <v>43</v>
-      </c>
-      <c r="S36" t="s">
-        <v>76</v>
-      </c>
-      <c r="T36" t="s">
-        <v>77</v>
-      </c>
-      <c r="U36" t="s">
-        <v>43</v>
-      </c>
-      <c r="X36">
+        <v>34</v>
+      </c>
+      <c r="P36" t="s">
+        <v>35</v>
+      </c>
+      <c r="W36" t="s">
+        <v>49</v>
+      </c>
+      <c r="X36" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB36">
         <v>3</v>
       </c>
     </row>
@@ -1947,21 +2079,21 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F37">
         <v>3</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H37" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I37" t="s">
-        <v>53</v>
-      </c>
-      <c r="X37">
+        <v>58</v>
+      </c>
+      <c r="AB37">
         <v>3</v>
       </c>
     </row>
@@ -1973,19 +2105,19 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F38">
         <v>-40</v>
       </c>
       <c r="G38" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I38" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
@@ -1996,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2008,30 +2140,33 @@
         <v>-25</v>
       </c>
       <c r="G39" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H39" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I39" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>30</v>
-      </c>
-      <c r="R39" t="s">
-        <v>43</v>
-      </c>
-      <c r="S39" t="s">
-        <v>70</v>
-      </c>
-      <c r="U39" t="s">
-        <v>31</v>
-      </c>
-      <c r="X39">
+        <v>34</v>
+      </c>
+      <c r="P39" t="s">
+        <v>78</v>
+      </c>
+      <c r="W39" t="s">
+        <v>49</v>
+      </c>
+      <c r="X39" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB39">
         <v>3</v>
       </c>
     </row>
@@ -2043,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -2055,30 +2190,33 @@
         <v>-25</v>
       </c>
       <c r="G40" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H40" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J40">
         <v>11</v>
       </c>
       <c r="K40" t="s">
-        <v>36</v>
-      </c>
-      <c r="R40" t="s">
-        <v>57</v>
-      </c>
-      <c r="S40" t="s">
-        <v>58</v>
-      </c>
-      <c r="U40" t="s">
-        <v>31</v>
-      </c>
-      <c r="X40">
+        <v>41</v>
+      </c>
+      <c r="P40" t="s">
+        <v>87</v>
+      </c>
+      <c r="W40" t="s">
+        <v>63</v>
+      </c>
+      <c r="X40" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB40">
         <v>3</v>
       </c>
     </row>
@@ -2090,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2102,30 +2240,33 @@
         <v>-36</v>
       </c>
       <c r="G41" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I41" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>30</v>
-      </c>
-      <c r="R41" t="s">
-        <v>57</v>
-      </c>
-      <c r="S41" t="s">
-        <v>58</v>
-      </c>
-      <c r="U41" t="s">
-        <v>43</v>
-      </c>
-      <c r="X41">
+        <v>34</v>
+      </c>
+      <c r="P41" t="s">
+        <v>62</v>
+      </c>
+      <c r="W41" t="s">
+        <v>63</v>
+      </c>
+      <c r="X41" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB41">
         <v>3</v>
       </c>
     </row>
@@ -2137,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2149,30 +2290,33 @@
         <v>-36</v>
       </c>
       <c r="G42" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H42" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I42" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J42">
         <v>33</v>
       </c>
       <c r="K42" t="s">
-        <v>36</v>
-      </c>
-      <c r="R42" t="s">
-        <v>43</v>
-      </c>
-      <c r="S42" t="s">
-        <v>40</v>
-      </c>
-      <c r="U42" t="s">
-        <v>43</v>
-      </c>
-      <c r="X42">
+        <v>41</v>
+      </c>
+      <c r="P42" t="s">
+        <v>78</v>
+      </c>
+      <c r="W42" t="s">
+        <v>49</v>
+      </c>
+      <c r="X42" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB42">
         <v>3</v>
       </c>
     </row>
@@ -2184,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2196,30 +2340,33 @@
         <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H43" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I43" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J43">
         <v>31</v>
       </c>
       <c r="K43" t="s">
-        <v>36</v>
-      </c>
-      <c r="R43" t="s">
-        <v>43</v>
-      </c>
-      <c r="S43" t="s">
-        <v>78</v>
-      </c>
-      <c r="U43" t="s">
-        <v>43</v>
-      </c>
-      <c r="X43">
+        <v>41</v>
+      </c>
+      <c r="P43" t="s">
+        <v>87</v>
+      </c>
+      <c r="W43" t="s">
+        <v>49</v>
+      </c>
+      <c r="X43" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB43">
         <v>3</v>
       </c>
     </row>
@@ -2231,21 +2378,21 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F44">
         <v>3</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I44" t="s">
-        <v>53</v>
-      </c>
-      <c r="X44">
+        <v>58</v>
+      </c>
+      <c r="AB44">
         <v>3</v>
       </c>
     </row>
@@ -2257,19 +2404,19 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F45">
         <v>-40</v>
       </c>
       <c r="G45" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H45" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I45" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
@@ -2280,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2292,33 +2439,36 @@
         <v>-20</v>
       </c>
       <c r="G46" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H46" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I46" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>36</v>
-      </c>
-      <c r="R46" t="s">
-        <v>31</v>
-      </c>
-      <c r="S46" t="s">
-        <v>70</v>
-      </c>
-      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="P46" t="s">
+        <v>35</v>
+      </c>
+      <c r="W46" t="s">
+        <v>36</v>
+      </c>
+      <c r="X46" t="s">
         <v>79</v>
       </c>
-      <c r="U46" t="s">
-        <v>31</v>
-      </c>
-      <c r="X46">
+      <c r="Y46" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB46">
         <v>4</v>
       </c>
     </row>
@@ -2330,7 +2480,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2342,33 +2492,36 @@
         <v>-21</v>
       </c>
       <c r="G47" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H47" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I47" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47" t="s">
-        <v>36</v>
-      </c>
-      <c r="R47" t="s">
-        <v>43</v>
-      </c>
-      <c r="S47" t="s">
-        <v>76</v>
-      </c>
-      <c r="T47" t="s">
-        <v>80</v>
-      </c>
-      <c r="U47" t="s">
-        <v>31</v>
-      </c>
-      <c r="X47">
+        <v>41</v>
+      </c>
+      <c r="P47" t="s">
+        <v>48</v>
+      </c>
+      <c r="W47" t="s">
+        <v>49</v>
+      </c>
+      <c r="X47" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB47">
         <v>4</v>
       </c>
     </row>
@@ -2380,7 +2533,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -2392,33 +2545,36 @@
         <v>-23</v>
       </c>
       <c r="G48" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H48" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I48" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J48">
         <v>6</v>
       </c>
       <c r="K48" t="s">
-        <v>36</v>
-      </c>
-      <c r="R48" t="s">
-        <v>43</v>
-      </c>
-      <c r="S48" t="s">
-        <v>70</v>
-      </c>
-      <c r="T48" t="s">
-        <v>81</v>
-      </c>
-      <c r="U48" t="s">
-        <v>31</v>
-      </c>
-      <c r="X48">
+        <v>41</v>
+      </c>
+      <c r="P48" t="s">
+        <v>35</v>
+      </c>
+      <c r="W48" t="s">
+        <v>49</v>
+      </c>
+      <c r="X48" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB48">
         <v>4</v>
       </c>
     </row>
@@ -2430,7 +2586,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D49">
         <v>4</v>
@@ -2442,18 +2598,18 @@
         <v>-29</v>
       </c>
       <c r="G49" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I49" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>36</v>
-      </c>
-      <c r="X49">
+        <v>41</v>
+      </c>
+      <c r="AB49">
         <v>4</v>
       </c>
     </row>
@@ -2465,7 +2621,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -2477,15 +2633,15 @@
         <v>-29</v>
       </c>
       <c r="G50" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H50" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I50" t="s">
-        <v>55</v>
-      </c>
-      <c r="X50">
+        <v>60</v>
+      </c>
+      <c r="AB50">
         <v>4</v>
       </c>
     </row>
@@ -2497,7 +2653,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2509,33 +2665,36 @@
         <v>-30</v>
       </c>
       <c r="G51" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H51" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J51">
         <v>5</v>
       </c>
       <c r="K51" t="s">
-        <v>36</v>
-      </c>
-      <c r="R51" t="s">
-        <v>31</v>
-      </c>
-      <c r="S51" t="s">
-        <v>82</v>
-      </c>
-      <c r="U51" t="s">
-        <v>31</v>
-      </c>
-      <c r="V51" t="s">
-        <v>31</v>
-      </c>
-      <c r="X51">
+        <v>41</v>
+      </c>
+      <c r="P51" t="s">
+        <v>92</v>
+      </c>
+      <c r="W51" t="s">
+        <v>36</v>
+      </c>
+      <c r="X51" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB51">
         <v>4</v>
       </c>
     </row>
@@ -2547,7 +2706,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -2559,30 +2718,33 @@
         <v>-35</v>
       </c>
       <c r="G52" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H52" t="s">
+        <v>39</v>
+      </c>
+      <c r="I52" t="s">
+        <v>40</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
         <v>34</v>
       </c>
-      <c r="I52" t="s">
+      <c r="P52" t="s">
         <v>35</v>
       </c>
-      <c r="J52">
-        <v>2</v>
-      </c>
-      <c r="K52" t="s">
-        <v>30</v>
-      </c>
-      <c r="R52" t="s">
-        <v>43</v>
-      </c>
-      <c r="S52" t="s">
-        <v>70</v>
-      </c>
-      <c r="U52" t="s">
-        <v>31</v>
-      </c>
-      <c r="X52">
+      <c r="W52" t="s">
+        <v>49</v>
+      </c>
+      <c r="X52" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB52">
         <v>4</v>
       </c>
     </row>
@@ -2594,7 +2756,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -2606,30 +2768,33 @@
         <v>-37</v>
       </c>
       <c r="G53" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H53" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I53" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J53">
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>36</v>
-      </c>
-      <c r="R53" t="s">
-        <v>31</v>
-      </c>
-      <c r="S53" t="s">
-        <v>40</v>
-      </c>
-      <c r="U53" t="s">
-        <v>43</v>
-      </c>
-      <c r="X53">
+        <v>41</v>
+      </c>
+      <c r="P53" t="s">
+        <v>48</v>
+      </c>
+      <c r="W53" t="s">
+        <v>36</v>
+      </c>
+      <c r="X53" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB53">
         <v>4</v>
       </c>
     </row>
@@ -2641,7 +2806,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2653,30 +2818,33 @@
         <v>48</v>
       </c>
       <c r="G54" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H54" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I54" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J54">
         <v>20</v>
       </c>
       <c r="K54" t="s">
-        <v>36</v>
-      </c>
-      <c r="R54" t="s">
-        <v>57</v>
-      </c>
-      <c r="S54" t="s">
-        <v>44</v>
-      </c>
-      <c r="U54" t="s">
-        <v>31</v>
-      </c>
-      <c r="X54">
+        <v>41</v>
+      </c>
+      <c r="P54" t="s">
+        <v>62</v>
+      </c>
+      <c r="W54" t="s">
+        <v>63</v>
+      </c>
+      <c r="X54" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB54">
         <v>4</v>
       </c>
     </row>
@@ -2688,7 +2856,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2700,30 +2868,33 @@
         <v>28</v>
       </c>
       <c r="G55" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H55" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I55" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J55">
         <v>12</v>
       </c>
       <c r="K55" t="s">
-        <v>36</v>
-      </c>
-      <c r="R55" t="s">
-        <v>57</v>
-      </c>
-      <c r="S55" t="s">
-        <v>58</v>
-      </c>
-      <c r="U55" t="s">
-        <v>43</v>
-      </c>
-      <c r="X55">
+        <v>41</v>
+      </c>
+      <c r="P55" t="s">
+        <v>87</v>
+      </c>
+      <c r="W55" t="s">
+        <v>63</v>
+      </c>
+      <c r="X55" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB55">
         <v>4</v>
       </c>
     </row>
@@ -2735,7 +2906,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2747,30 +2918,33 @@
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H56" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I56" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>30</v>
-      </c>
-      <c r="R56" t="s">
-        <v>43</v>
-      </c>
-      <c r="S56" t="s">
-        <v>49</v>
-      </c>
-      <c r="U56" t="s">
-        <v>31</v>
-      </c>
-      <c r="X56">
+        <v>34</v>
+      </c>
+      <c r="P56" t="s">
+        <v>48</v>
+      </c>
+      <c r="W56" t="s">
+        <v>49</v>
+      </c>
+      <c r="X56" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB56">
         <v>4</v>
       </c>
     </row>
@@ -2782,7 +2956,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2794,30 +2968,33 @@
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H57" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I57" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J57">
         <v>5</v>
       </c>
       <c r="K57" t="s">
-        <v>36</v>
-      </c>
-      <c r="R57" t="s">
-        <v>57</v>
-      </c>
-      <c r="S57" t="s">
-        <v>58</v>
-      </c>
-      <c r="U57" t="s">
-        <v>43</v>
-      </c>
-      <c r="X57">
+        <v>41</v>
+      </c>
+      <c r="P57" t="s">
+        <v>62</v>
+      </c>
+      <c r="W57" t="s">
+        <v>63</v>
+      </c>
+      <c r="X57" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB57">
         <v>4</v>
       </c>
     </row>
@@ -2829,7 +3006,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -2841,30 +3018,33 @@
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H58" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I58" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J58">
         <v>10</v>
       </c>
       <c r="K58" t="s">
-        <v>36</v>
-      </c>
-      <c r="R58" t="s">
-        <v>31</v>
-      </c>
-      <c r="S58" t="s">
-        <v>83</v>
-      </c>
-      <c r="U58" t="s">
-        <v>43</v>
-      </c>
-      <c r="X58">
+        <v>41</v>
+      </c>
+      <c r="P58" t="s">
+        <v>35</v>
+      </c>
+      <c r="W58" t="s">
+        <v>36</v>
+      </c>
+      <c r="X58" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB58">
         <v>4</v>
       </c>
     </row>
@@ -2876,7 +3056,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2888,30 +3068,33 @@
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H59" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I59" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>36</v>
-      </c>
-      <c r="R59" t="s">
-        <v>31</v>
-      </c>
-      <c r="S59" t="s">
-        <v>84</v>
-      </c>
-      <c r="U59" t="s">
-        <v>31</v>
-      </c>
-      <c r="X59">
+        <v>41</v>
+      </c>
+      <c r="P59" t="s">
+        <v>69</v>
+      </c>
+      <c r="W59" t="s">
+        <v>36</v>
+      </c>
+      <c r="X59" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB59">
         <v>4</v>
       </c>
     </row>
@@ -2923,21 +3106,21 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F60">
         <v>3</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H60" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I60" t="s">
-        <v>53</v>
-      </c>
-      <c r="X60">
+        <v>58</v>
+      </c>
+      <c r="AB60">
         <v>4</v>
       </c>
     </row>
@@ -2949,19 +3132,19 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F61">
         <v>-40</v>
       </c>
       <c r="G61" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H61" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I61" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -2972,7 +3155,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2984,33 +3167,36 @@
         <v>-20</v>
       </c>
       <c r="G62" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H62" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I62" t="s">
+        <v>40</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62" t="s">
+        <v>41</v>
+      </c>
+      <c r="P62" t="s">
         <v>35</v>
       </c>
-      <c r="J62">
-        <v>1</v>
-      </c>
-      <c r="K62" t="s">
-        <v>36</v>
-      </c>
-      <c r="R62" t="s">
-        <v>43</v>
-      </c>
-      <c r="S62" t="s">
-        <v>32</v>
-      </c>
-      <c r="T62" t="s">
-        <v>85</v>
-      </c>
-      <c r="U62" t="s">
-        <v>31</v>
-      </c>
-      <c r="X62">
+      <c r="W62" t="s">
+        <v>49</v>
+      </c>
+      <c r="X62" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB62">
         <v>5</v>
       </c>
     </row>
@@ -3022,7 +3208,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -3034,36 +3220,39 @@
         <v>-21</v>
       </c>
       <c r="G63" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H63" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I63" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>36</v>
-      </c>
-      <c r="R63" t="s">
-        <v>43</v>
-      </c>
-      <c r="S63" t="s">
-        <v>40</v>
-      </c>
-      <c r="T63" t="s">
-        <v>74</v>
-      </c>
-      <c r="U63" t="s">
-        <v>43</v>
-      </c>
-      <c r="V63" t="s">
-        <v>43</v>
-      </c>
-      <c r="X63">
+        <v>41</v>
+      </c>
+      <c r="P63" t="s">
+        <v>35</v>
+      </c>
+      <c r="W63" t="s">
+        <v>49</v>
+      </c>
+      <c r="X63" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB63">
         <v>5</v>
       </c>
     </row>
@@ -3075,7 +3264,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -3087,33 +3276,36 @@
         <v>-21</v>
       </c>
       <c r="G64" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H64" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I64" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J64">
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>30</v>
-      </c>
-      <c r="R64" t="s">
-        <v>43</v>
-      </c>
-      <c r="S64" t="s">
-        <v>44</v>
-      </c>
-      <c r="T64" t="s">
-        <v>45</v>
-      </c>
-      <c r="U64" t="s">
-        <v>43</v>
-      </c>
-      <c r="X64">
+        <v>34</v>
+      </c>
+      <c r="P64" t="s">
+        <v>48</v>
+      </c>
+      <c r="W64" t="s">
+        <v>49</v>
+      </c>
+      <c r="X64" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB64">
         <v>5</v>
       </c>
     </row>
@@ -3125,7 +3317,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3137,33 +3329,36 @@
         <v>-36</v>
       </c>
       <c r="G65" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H65" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I65" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J65">
         <v>3</v>
       </c>
       <c r="K65" t="s">
-        <v>36</v>
-      </c>
-      <c r="R65" t="s">
-        <v>43</v>
-      </c>
-      <c r="S65" t="s">
-        <v>46</v>
-      </c>
-      <c r="T65" t="s">
-        <v>86</v>
-      </c>
-      <c r="U65" t="s">
-        <v>43</v>
-      </c>
-      <c r="X65">
+        <v>41</v>
+      </c>
+      <c r="P65" t="s">
+        <v>87</v>
+      </c>
+      <c r="W65" t="s">
+        <v>49</v>
+      </c>
+      <c r="X65" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB65">
         <v>5</v>
       </c>
     </row>
@@ -3175,7 +3370,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -3187,33 +3382,36 @@
         <v>-39</v>
       </c>
       <c r="G66" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H66" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I66" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J66">
         <v>8</v>
       </c>
       <c r="K66" t="s">
-        <v>30</v>
-      </c>
-      <c r="R66" t="s">
-        <v>43</v>
-      </c>
-      <c r="S66" t="s">
-        <v>40</v>
-      </c>
-      <c r="T66" t="s">
-        <v>85</v>
-      </c>
-      <c r="U66" t="s">
-        <v>43</v>
-      </c>
-      <c r="X66">
+        <v>34</v>
+      </c>
+      <c r="P66" t="s">
+        <v>87</v>
+      </c>
+      <c r="W66" t="s">
+        <v>49</v>
+      </c>
+      <c r="X66" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB66">
         <v>5</v>
       </c>
     </row>
@@ -3225,7 +3423,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3237,33 +3435,36 @@
         <v>-47</v>
       </c>
       <c r="G67" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H67" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I67" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J67">
         <v>8</v>
       </c>
       <c r="K67" t="s">
-        <v>30</v>
-      </c>
-      <c r="R67" t="s">
-        <v>31</v>
-      </c>
-      <c r="S67" t="s">
-        <v>76</v>
-      </c>
-      <c r="T67" t="s">
-        <v>42</v>
-      </c>
-      <c r="U67" t="s">
-        <v>31</v>
-      </c>
-      <c r="X67">
+        <v>34</v>
+      </c>
+      <c r="P67" t="s">
+        <v>35</v>
+      </c>
+      <c r="W67" t="s">
+        <v>36</v>
+      </c>
+      <c r="X67" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB67">
         <v>5</v>
       </c>
     </row>
@@ -3275,7 +3476,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -3287,33 +3488,36 @@
         <v>45</v>
       </c>
       <c r="G68" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H68" t="s">
+        <v>39</v>
+      </c>
+      <c r="I68" t="s">
+        <v>40</v>
+      </c>
+      <c r="J68">
+        <v>2</v>
+      </c>
+      <c r="K68" t="s">
         <v>34</v>
       </c>
-      <c r="I68" t="s">
-        <v>35</v>
-      </c>
-      <c r="J68">
-        <v>2</v>
-      </c>
-      <c r="K68" t="s">
-        <v>30</v>
-      </c>
-      <c r="R68" t="s">
-        <v>43</v>
-      </c>
-      <c r="S68" t="s">
-        <v>40</v>
-      </c>
-      <c r="T68" t="s">
-        <v>87</v>
-      </c>
-      <c r="U68" t="s">
-        <v>31</v>
-      </c>
-      <c r="X68">
+      <c r="P68" t="s">
+        <v>48</v>
+      </c>
+      <c r="W68" t="s">
+        <v>49</v>
+      </c>
+      <c r="X68" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB68">
         <v>5</v>
       </c>
     </row>
@@ -3325,7 +3529,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3337,36 +3541,39 @@
         <v>43</v>
       </c>
       <c r="G69" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H69" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I69" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J69">
         <v>28</v>
       </c>
       <c r="K69" t="s">
-        <v>30</v>
-      </c>
-      <c r="R69" t="s">
-        <v>43</v>
-      </c>
-      <c r="S69" t="s">
-        <v>46</v>
-      </c>
-      <c r="T69" t="s">
-        <v>66</v>
-      </c>
-      <c r="U69" t="s">
-        <v>31</v>
-      </c>
-      <c r="V69" t="s">
-        <v>31</v>
-      </c>
-      <c r="X69">
+        <v>34</v>
+      </c>
+      <c r="P69" t="s">
+        <v>48</v>
+      </c>
+      <c r="W69" t="s">
+        <v>49</v>
+      </c>
+      <c r="X69" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB69">
         <v>5</v>
       </c>
     </row>
@@ -3378,7 +3585,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3390,33 +3597,36 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H70" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I70" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J70">
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>36</v>
-      </c>
-      <c r="R70" t="s">
-        <v>31</v>
-      </c>
-      <c r="S70" t="s">
-        <v>88</v>
-      </c>
-      <c r="T70" t="s">
-        <v>85</v>
-      </c>
-      <c r="U70" t="s">
-        <v>31</v>
-      </c>
-      <c r="X70">
+        <v>41</v>
+      </c>
+      <c r="P70" t="s">
+        <v>99</v>
+      </c>
+      <c r="W70" t="s">
+        <v>36</v>
+      </c>
+      <c r="X70" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB70">
         <v>5</v>
       </c>
     </row>
@@ -3428,7 +3638,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -3440,33 +3650,36 @@
         <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H71" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I71" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J71">
         <v>13</v>
       </c>
       <c r="K71" t="s">
-        <v>30</v>
-      </c>
-      <c r="R71" t="s">
-        <v>43</v>
-      </c>
-      <c r="S71" t="s">
-        <v>37</v>
-      </c>
-      <c r="T71" t="s">
-        <v>89</v>
-      </c>
-      <c r="U71" t="s">
-        <v>43</v>
-      </c>
-      <c r="X71">
+        <v>34</v>
+      </c>
+      <c r="P71" t="s">
+        <v>48</v>
+      </c>
+      <c r="W71" t="s">
+        <v>49</v>
+      </c>
+      <c r="X71" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB71">
         <v>5</v>
       </c>
     </row>
@@ -3478,21 +3691,21 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F72">
         <v>3</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H72" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I72" t="s">
-        <v>53</v>
-      </c>
-      <c r="X72">
+        <v>58</v>
+      </c>
+      <c r="AB72">
         <v>5</v>
       </c>
     </row>
@@ -3504,19 +3717,19 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F73">
         <v>-40</v>
       </c>
       <c r="G73" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H73" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I73" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74">
@@ -3527,7 +3740,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3539,30 +3752,33 @@
         <v>-32</v>
       </c>
       <c r="G74" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H74" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I74" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J74">
         <v>6</v>
       </c>
       <c r="K74" t="s">
-        <v>36</v>
-      </c>
-      <c r="R74" t="s">
-        <v>43</v>
-      </c>
-      <c r="S74" t="s">
-        <v>60</v>
-      </c>
-      <c r="U74" t="s">
-        <v>31</v>
-      </c>
-      <c r="X74">
+        <v>41</v>
+      </c>
+      <c r="P74" t="s">
+        <v>48</v>
+      </c>
+      <c r="W74" t="s">
+        <v>49</v>
+      </c>
+      <c r="X74" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB74">
         <v>5</v>
       </c>
     </row>
@@ -3574,7 +3790,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -3586,30 +3802,33 @@
         <v>-38</v>
       </c>
       <c r="G75" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H75" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I75" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="J75">
         <v>-2</v>
       </c>
       <c r="K75" t="s">
-        <v>30</v>
-      </c>
-      <c r="R75" t="s">
-        <v>57</v>
-      </c>
-      <c r="S75" t="s">
-        <v>58</v>
-      </c>
-      <c r="U75" t="s">
-        <v>43</v>
-      </c>
-      <c r="X75">
+        <v>34</v>
+      </c>
+      <c r="P75" t="s">
+        <v>62</v>
+      </c>
+      <c r="W75" t="s">
+        <v>63</v>
+      </c>
+      <c r="X75" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB75">
         <v>5</v>
       </c>
     </row>
@@ -3621,7 +3840,7 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -3633,30 +3852,33 @@
         <v>-36</v>
       </c>
       <c r="G76" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H76" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I76" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J76">
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>30</v>
-      </c>
-      <c r="R76" t="s">
-        <v>31</v>
-      </c>
-      <c r="S76" t="s">
-        <v>70</v>
-      </c>
-      <c r="U76" t="s">
-        <v>31</v>
-      </c>
-      <c r="X76">
+        <v>34</v>
+      </c>
+      <c r="P76" t="s">
+        <v>35</v>
+      </c>
+      <c r="W76" t="s">
+        <v>36</v>
+      </c>
+      <c r="X76" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB76">
         <v>5</v>
       </c>
     </row>
@@ -3668,7 +3890,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D77">
         <v>4</v>
@@ -3680,15 +3902,15 @@
         <v>-36</v>
       </c>
       <c r="G77" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H77" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I77" t="s">
-        <v>55</v>
-      </c>
-      <c r="X77">
+        <v>60</v>
+      </c>
+      <c r="AB77">
         <v>5</v>
       </c>
     </row>
@@ -3700,7 +3922,7 @@
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3712,33 +3934,36 @@
         <v>-31</v>
       </c>
       <c r="G78" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H78" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I78" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>36</v>
-      </c>
-      <c r="R78" t="s">
-        <v>43</v>
-      </c>
-      <c r="S78" t="s">
-        <v>44</v>
-      </c>
-      <c r="T78" t="s">
-        <v>66</v>
-      </c>
-      <c r="U78" t="s">
-        <v>43</v>
-      </c>
-      <c r="X78">
+        <v>41</v>
+      </c>
+      <c r="P78" t="s">
+        <v>35</v>
+      </c>
+      <c r="W78" t="s">
+        <v>49</v>
+      </c>
+      <c r="X78" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB78">
         <v>6</v>
       </c>
     </row>
@@ -3750,7 +3975,7 @@
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -3762,33 +3987,36 @@
         <v>-31</v>
       </c>
       <c r="G79" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H79" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I79" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>36</v>
-      </c>
-      <c r="R79" t="s">
-        <v>31</v>
-      </c>
-      <c r="S79" t="s">
-        <v>88</v>
-      </c>
-      <c r="T79" t="s">
-        <v>45</v>
-      </c>
-      <c r="U79" t="s">
-        <v>43</v>
-      </c>
-      <c r="X79">
+        <v>41</v>
+      </c>
+      <c r="P79" t="s">
+        <v>99</v>
+      </c>
+      <c r="W79" t="s">
+        <v>36</v>
+      </c>
+      <c r="X79" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB79">
         <v>6</v>
       </c>
     </row>
@@ -3800,7 +4028,7 @@
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -3812,33 +4040,36 @@
         <v>-31</v>
       </c>
       <c r="G80" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H80" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I80" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J80">
         <v>5</v>
       </c>
       <c r="K80" t="s">
-        <v>36</v>
-      </c>
-      <c r="R80" t="s">
-        <v>43</v>
-      </c>
-      <c r="S80" t="s">
-        <v>46</v>
-      </c>
-      <c r="T80" t="s">
-        <v>85</v>
-      </c>
-      <c r="U80" t="s">
-        <v>31</v>
-      </c>
-      <c r="X80">
+        <v>41</v>
+      </c>
+      <c r="P80" t="s">
+        <v>35</v>
+      </c>
+      <c r="W80" t="s">
+        <v>49</v>
+      </c>
+      <c r="X80" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB80">
         <v>6</v>
       </c>
     </row>
@@ -3850,7 +4081,7 @@
         <v>2</v>
       </c>
       <c r="C81" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D81">
         <v>4</v>
@@ -3862,15 +4093,15 @@
         <v>-36</v>
       </c>
       <c r="G81" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H81" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I81" t="s">
-        <v>55</v>
-      </c>
-      <c r="X81">
+        <v>60</v>
+      </c>
+      <c r="AB81">
         <v>6</v>
       </c>
     </row>
@@ -3882,7 +4113,7 @@
         <v>2</v>
       </c>
       <c r="C82" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3894,30 +4125,33 @@
         <v>-45</v>
       </c>
       <c r="G82" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H82" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I82" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J82">
         <v>6</v>
       </c>
       <c r="K82" t="s">
-        <v>36</v>
-      </c>
-      <c r="R82" t="s">
-        <v>31</v>
-      </c>
-      <c r="S82" t="s">
+        <v>41</v>
+      </c>
+      <c r="P82" t="s">
         <v>92</v>
       </c>
-      <c r="U82" t="s">
-        <v>43</v>
-      </c>
-      <c r="X82">
+      <c r="W82" t="s">
+        <v>36</v>
+      </c>
+      <c r="X82" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB82">
         <v>6</v>
       </c>
     </row>
@@ -3929,7 +4163,7 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -3941,30 +4175,33 @@
         <v>49</v>
       </c>
       <c r="G83" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H83" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I83" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>30</v>
-      </c>
-      <c r="R83" t="s">
-        <v>57</v>
-      </c>
-      <c r="S83" t="s">
-        <v>44</v>
-      </c>
-      <c r="U83" t="s">
-        <v>43</v>
-      </c>
-      <c r="X83">
+        <v>34</v>
+      </c>
+      <c r="P83" t="s">
+        <v>62</v>
+      </c>
+      <c r="W83" t="s">
+        <v>63</v>
+      </c>
+      <c r="X83" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB83">
         <v>6</v>
       </c>
     </row>
@@ -3976,7 +4213,7 @@
         <v>2</v>
       </c>
       <c r="C84" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -3988,30 +4225,33 @@
         <v>49</v>
       </c>
       <c r="G84" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H84" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I84" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>30</v>
-      </c>
-      <c r="R84" t="s">
-        <v>31</v>
-      </c>
-      <c r="S84" t="s">
-        <v>82</v>
-      </c>
-      <c r="U84" t="s">
-        <v>31</v>
-      </c>
-      <c r="X84">
+        <v>34</v>
+      </c>
+      <c r="P84" t="s">
+        <v>92</v>
+      </c>
+      <c r="W84" t="s">
+        <v>36</v>
+      </c>
+      <c r="X84" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB84">
         <v>6</v>
       </c>
     </row>
@@ -4023,7 +4263,7 @@
         <v>2</v>
       </c>
       <c r="C85" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D85">
         <v>4</v>
@@ -4035,15 +4275,15 @@
         <v>49</v>
       </c>
       <c r="G85" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H85" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I85" t="s">
-        <v>55</v>
-      </c>
-      <c r="X85">
+        <v>60</v>
+      </c>
+      <c r="AB85">
         <v>6</v>
       </c>
     </row>
@@ -4055,7 +4295,7 @@
         <v>2</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -4067,33 +4307,36 @@
         <v>-3</v>
       </c>
       <c r="G86" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H86" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I86" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>36</v>
-      </c>
-      <c r="R86" t="s">
-        <v>43</v>
-      </c>
-      <c r="S86" t="s">
-        <v>93</v>
-      </c>
-      <c r="T86" t="s">
-        <v>94</v>
-      </c>
-      <c r="U86" t="s">
-        <v>31</v>
-      </c>
-      <c r="X86">
+        <v>41</v>
+      </c>
+      <c r="P86" t="s">
+        <v>105</v>
+      </c>
+      <c r="W86" t="s">
+        <v>49</v>
+      </c>
+      <c r="X86" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB86">
         <v>7</v>
       </c>
     </row>
@@ -4105,21 +4348,21 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F87">
         <v>-40</v>
       </c>
       <c r="G87" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H87" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I87" t="s">
-        <v>55</v>
-      </c>
-      <c r="X87">
+        <v>60</v>
+      </c>
+      <c r="AB87">
         <v>7</v>
       </c>
     </row>
@@ -4131,7 +4374,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4143,30 +4386,33 @@
         <v>-25</v>
       </c>
       <c r="G88" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H88" t="s">
+        <v>39</v>
+      </c>
+      <c r="I88" t="s">
+        <v>40</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88" t="s">
         <v>34</v>
       </c>
-      <c r="I88" t="s">
-        <v>35</v>
-      </c>
-      <c r="J88">
-        <v>1</v>
-      </c>
-      <c r="K88" t="s">
-        <v>30</v>
-      </c>
-      <c r="R88" t="s">
-        <v>57</v>
-      </c>
-      <c r="S88" t="s">
-        <v>58</v>
-      </c>
-      <c r="U88" t="s">
-        <v>43</v>
-      </c>
-      <c r="X88">
+      <c r="P88" t="s">
+        <v>62</v>
+      </c>
+      <c r="W88" t="s">
+        <v>63</v>
+      </c>
+      <c r="X88" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB88">
         <v>6</v>
       </c>
     </row>
@@ -4178,7 +4424,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4190,30 +4436,33 @@
         <v>-26</v>
       </c>
       <c r="G89" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H89" t="s">
+        <v>39</v>
+      </c>
+      <c r="I89" t="s">
+        <v>40</v>
+      </c>
+      <c r="J89">
+        <v>2</v>
+      </c>
+      <c r="K89" t="s">
         <v>34</v>
       </c>
-      <c r="I89" t="s">
-        <v>35</v>
-      </c>
-      <c r="J89">
-        <v>2</v>
-      </c>
-      <c r="K89" t="s">
-        <v>30</v>
-      </c>
-      <c r="R89" t="s">
-        <v>57</v>
-      </c>
-      <c r="S89" t="s">
-        <v>58</v>
-      </c>
-      <c r="U89" t="s">
-        <v>43</v>
-      </c>
-      <c r="X89">
+      <c r="P89" t="s">
+        <v>87</v>
+      </c>
+      <c r="W89" t="s">
+        <v>63</v>
+      </c>
+      <c r="X89" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB89">
         <v>6</v>
       </c>
     </row>
@@ -4225,7 +4474,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -4237,30 +4486,33 @@
         <v>-28</v>
       </c>
       <c r="G90" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H90" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I90" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J90">
         <v>7</v>
       </c>
       <c r="K90" t="s">
-        <v>36</v>
-      </c>
-      <c r="R90" t="s">
-        <v>31</v>
-      </c>
-      <c r="S90" t="s">
-        <v>70</v>
-      </c>
-      <c r="U90" t="s">
-        <v>31</v>
-      </c>
-      <c r="X90">
+        <v>41</v>
+      </c>
+      <c r="P90" t="s">
+        <v>35</v>
+      </c>
+      <c r="W90" t="s">
+        <v>36</v>
+      </c>
+      <c r="X90" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB90">
         <v>6</v>
       </c>
     </row>
@@ -4272,7 +4524,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4284,30 +4536,33 @@
         <v>-35</v>
       </c>
       <c r="G91" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H91" t="s">
+        <v>39</v>
+      </c>
+      <c r="I91" t="s">
+        <v>40</v>
+      </c>
+      <c r="J91">
+        <v>3</v>
+      </c>
+      <c r="K91" t="s">
         <v>34</v>
       </c>
-      <c r="I91" t="s">
-        <v>35</v>
-      </c>
-      <c r="J91">
-        <v>3</v>
-      </c>
-      <c r="K91" t="s">
-        <v>30</v>
-      </c>
-      <c r="R91" t="s">
-        <v>31</v>
-      </c>
-      <c r="S91" t="s">
-        <v>84</v>
-      </c>
-      <c r="U91" t="s">
-        <v>31</v>
-      </c>
-      <c r="X91">
+      <c r="P91" t="s">
+        <v>87</v>
+      </c>
+      <c r="W91" t="s">
+        <v>36</v>
+      </c>
+      <c r="X91" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB91">
         <v>6</v>
       </c>
     </row>
@@ -4319,7 +4574,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -4331,30 +4586,33 @@
         <v>-38</v>
       </c>
       <c r="G92" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H92" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I92" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J92">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>30</v>
-      </c>
-      <c r="R92" t="s">
-        <v>31</v>
-      </c>
-      <c r="S92" t="s">
-        <v>70</v>
-      </c>
-      <c r="U92" t="s">
-        <v>31</v>
-      </c>
-      <c r="X92">
+        <v>34</v>
+      </c>
+      <c r="P92" t="s">
+        <v>35</v>
+      </c>
+      <c r="W92" t="s">
+        <v>36</v>
+      </c>
+      <c r="X92" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB92">
         <v>6</v>
       </c>
     </row>
@@ -4366,7 +4624,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D93">
         <v>3</v>
@@ -4378,30 +4636,33 @@
         <v>-39</v>
       </c>
       <c r="G93" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H93" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I93" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>30</v>
-      </c>
-      <c r="R93" t="s">
-        <v>57</v>
-      </c>
-      <c r="S93" t="s">
-        <v>44</v>
-      </c>
-      <c r="U93" t="s">
-        <v>31</v>
-      </c>
-      <c r="X93">
+        <v>34</v>
+      </c>
+      <c r="P93" t="s">
+        <v>62</v>
+      </c>
+      <c r="W93" t="s">
+        <v>63</v>
+      </c>
+      <c r="X93" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB93">
         <v>6</v>
       </c>
     </row>
@@ -4413,7 +4674,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D94">
         <v>4</v>
@@ -4425,15 +4686,15 @@
         <v>-39</v>
       </c>
       <c r="G94" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H94" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I94" t="s">
-        <v>55</v>
-      </c>
-      <c r="X94">
+        <v>60</v>
+      </c>
+      <c r="AB94">
         <v>6</v>
       </c>
     </row>
@@ -4445,7 +4706,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -4457,33 +4718,36 @@
         <v>-14</v>
       </c>
       <c r="G95" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H95" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I95" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J95">
         <v>-2</v>
       </c>
       <c r="K95" t="s">
-        <v>36</v>
-      </c>
-      <c r="R95" t="s">
-        <v>43</v>
-      </c>
-      <c r="S95" t="s">
-        <v>46</v>
-      </c>
-      <c r="T95" t="s">
-        <v>85</v>
-      </c>
-      <c r="U95" t="s">
-        <v>31</v>
-      </c>
-      <c r="X95">
+        <v>41</v>
+      </c>
+      <c r="P95" t="s">
+        <v>87</v>
+      </c>
+      <c r="W95" t="s">
+        <v>49</v>
+      </c>
+      <c r="X95" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB95">
         <v>8</v>
       </c>
     </row>
@@ -4495,7 +4759,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -4507,33 +4771,36 @@
         <v>-12</v>
       </c>
       <c r="G96" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H96" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I96" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J96">
         <v>-2</v>
       </c>
       <c r="K96" t="s">
-        <v>36</v>
-      </c>
-      <c r="R96" t="s">
-        <v>43</v>
-      </c>
-      <c r="S96" t="s">
-        <v>44</v>
-      </c>
-      <c r="T96" t="s">
-        <v>95</v>
-      </c>
-      <c r="U96" t="s">
-        <v>31</v>
-      </c>
-      <c r="X96">
+        <v>41</v>
+      </c>
+      <c r="P96" t="s">
+        <v>35</v>
+      </c>
+      <c r="W96" t="s">
+        <v>49</v>
+      </c>
+      <c r="X96" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB96">
         <v>8</v>
       </c>
     </row>
@@ -4545,7 +4812,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -4557,33 +4824,36 @@
         <v>-10</v>
       </c>
       <c r="G97" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H97" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I97" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>36</v>
-      </c>
-      <c r="R97" t="s">
-        <v>43</v>
-      </c>
-      <c r="S97" t="s">
-        <v>46</v>
-      </c>
-      <c r="T97" t="s">
-        <v>42</v>
-      </c>
-      <c r="U97" t="s">
-        <v>31</v>
-      </c>
-      <c r="X97">
+        <v>41</v>
+      </c>
+      <c r="P97" t="s">
+        <v>48</v>
+      </c>
+      <c r="W97" t="s">
+        <v>49</v>
+      </c>
+      <c r="X97" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB97">
         <v>8</v>
       </c>
     </row>
@@ -4595,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99">
@@ -4606,7 +4876,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -4618,30 +4888,33 @@
         <v>-45</v>
       </c>
       <c r="G99" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H99" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I99" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>30</v>
-      </c>
-      <c r="R99" t="s">
-        <v>31</v>
-      </c>
-      <c r="S99" t="s">
-        <v>60</v>
-      </c>
-      <c r="U99" t="s">
-        <v>43</v>
-      </c>
-      <c r="X99">
+        <v>34</v>
+      </c>
+      <c r="P99" t="s">
+        <v>48</v>
+      </c>
+      <c r="W99" t="s">
+        <v>36</v>
+      </c>
+      <c r="X99" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB99">
         <v>8</v>
       </c>
     </row>
@@ -4653,7 +4926,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D100">
         <v>4</v>
@@ -4665,15 +4938,15 @@
         <v>-33</v>
       </c>
       <c r="G100" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H100" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I100" t="s">
-        <v>53</v>
-      </c>
-      <c r="X100">
+        <v>58</v>
+      </c>
+      <c r="AB100">
         <v>7</v>
       </c>
     </row>
@@ -4685,21 +4958,21 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F101">
         <v>-40</v>
       </c>
       <c r="G101" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H101" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I101" t="s">
-        <v>55</v>
-      </c>
-      <c r="X101">
+        <v>60</v>
+      </c>
+      <c r="AB101">
         <v>9</v>
       </c>
     </row>
@@ -4711,7 +4984,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4723,30 +4996,33 @@
         <v>-30</v>
       </c>
       <c r="G102" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H102" t="s">
+        <v>39</v>
+      </c>
+      <c r="I102" t="s">
+        <v>40</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102" t="s">
         <v>34</v>
       </c>
-      <c r="I102" t="s">
-        <v>35</v>
-      </c>
-      <c r="J102">
-        <v>1</v>
-      </c>
-      <c r="K102" t="s">
-        <v>30</v>
-      </c>
-      <c r="R102" t="s">
-        <v>43</v>
-      </c>
-      <c r="S102" t="s">
-        <v>40</v>
-      </c>
-      <c r="U102" t="s">
-        <v>31</v>
-      </c>
-      <c r="X102">
+      <c r="P102" t="s">
+        <v>48</v>
+      </c>
+      <c r="W102" t="s">
+        <v>49</v>
+      </c>
+      <c r="X102" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB102">
         <v>8</v>
       </c>
     </row>
@@ -4758,7 +5034,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -4770,30 +5046,33 @@
         <v>-31</v>
       </c>
       <c r="G103" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H103" t="s">
+        <v>39</v>
+      </c>
+      <c r="I103" t="s">
+        <v>40</v>
+      </c>
+      <c r="J103">
+        <v>2</v>
+      </c>
+      <c r="K103" t="s">
         <v>34</v>
       </c>
-      <c r="I103" t="s">
+      <c r="P103" t="s">
         <v>35</v>
       </c>
-      <c r="J103">
-        <v>2</v>
-      </c>
-      <c r="K103" t="s">
-        <v>30</v>
-      </c>
-      <c r="R103" t="s">
-        <v>31</v>
-      </c>
-      <c r="S103" t="s">
-        <v>70</v>
-      </c>
-      <c r="U103" t="s">
-        <v>31</v>
-      </c>
-      <c r="X103">
+      <c r="W103" t="s">
+        <v>36</v>
+      </c>
+      <c r="X103" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB103">
         <v>8</v>
       </c>
     </row>
@@ -4805,7 +5084,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D104">
         <v>3</v>
@@ -4817,30 +5096,33 @@
         <v>-33</v>
       </c>
       <c r="G104" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H104" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I104" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>30</v>
-      </c>
-      <c r="R104" t="s">
-        <v>31</v>
-      </c>
-      <c r="S104" t="s">
-        <v>70</v>
-      </c>
-      <c r="U104" t="s">
-        <v>31</v>
-      </c>
-      <c r="X104">
+        <v>34</v>
+      </c>
+      <c r="P104" t="s">
+        <v>35</v>
+      </c>
+      <c r="W104" t="s">
+        <v>36</v>
+      </c>
+      <c r="X104" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB104">
         <v>8</v>
       </c>
     </row>
@@ -4852,7 +5134,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D105">
         <v>4</v>
@@ -4864,15 +5146,15 @@
         <v>-33</v>
       </c>
       <c r="G105" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H105" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I105" t="s">
-        <v>97</v>
-      </c>
-      <c r="X105">
+        <v>110</v>
+      </c>
+      <c r="AB105">
         <v>8</v>
       </c>
     </row>
@@ -4884,7 +5166,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -4896,36 +5178,39 @@
         <v>-48</v>
       </c>
       <c r="G106" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H106" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I106" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J106">
         <v>-9</v>
       </c>
       <c r="K106" t="s">
-        <v>36</v>
-      </c>
-      <c r="R106" t="s">
-        <v>43</v>
-      </c>
-      <c r="S106" t="s">
-        <v>44</v>
-      </c>
-      <c r="T106" t="s">
-        <v>98</v>
-      </c>
-      <c r="U106" t="s">
-        <v>43</v>
-      </c>
-      <c r="V106" t="s">
-        <v>43</v>
-      </c>
-      <c r="X106">
+        <v>41</v>
+      </c>
+      <c r="P106" t="s">
+        <v>35</v>
+      </c>
+      <c r="W106" t="s">
+        <v>49</v>
+      </c>
+      <c r="X106" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB106">
         <v>10</v>
       </c>
     </row>
@@ -4937,7 +5222,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -4949,33 +5234,36 @@
         <v>-39</v>
       </c>
       <c r="G107" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H107" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I107" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>36</v>
-      </c>
-      <c r="R107" t="s">
-        <v>31</v>
-      </c>
-      <c r="S107" t="s">
-        <v>46</v>
-      </c>
-      <c r="T107" t="s">
-        <v>42</v>
-      </c>
-      <c r="U107" t="s">
-        <v>31</v>
-      </c>
-      <c r="X107">
+        <v>41</v>
+      </c>
+      <c r="P107" t="s">
+        <v>35</v>
+      </c>
+      <c r="W107" t="s">
+        <v>36</v>
+      </c>
+      <c r="X107" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB107">
         <v>10</v>
       </c>
     </row>
@@ -4987,7 +5275,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D108">
         <v>3</v>
@@ -4999,33 +5287,36 @@
         <v>-39</v>
       </c>
       <c r="G108" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H108" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I108" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J108">
         <v>9</v>
       </c>
       <c r="K108" t="s">
-        <v>36</v>
-      </c>
-      <c r="R108" t="s">
-        <v>31</v>
-      </c>
-      <c r="S108" t="s">
-        <v>32</v>
-      </c>
-      <c r="T108" t="s">
-        <v>74</v>
-      </c>
-      <c r="U108" t="s">
-        <v>31</v>
-      </c>
-      <c r="X108">
+        <v>41</v>
+      </c>
+      <c r="P108" t="s">
+        <v>35</v>
+      </c>
+      <c r="W108" t="s">
+        <v>36</v>
+      </c>
+      <c r="X108" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB108">
         <v>10</v>
       </c>
     </row>
@@ -5037,7 +5328,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D109">
         <v>4</v>
@@ -5049,33 +5340,36 @@
         <v>-48</v>
       </c>
       <c r="G109" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H109" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I109" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>30</v>
-      </c>
-      <c r="R109" t="s">
-        <v>43</v>
-      </c>
-      <c r="S109" t="s">
-        <v>46</v>
-      </c>
-      <c r="T109" t="s">
-        <v>45</v>
-      </c>
-      <c r="U109" t="s">
-        <v>43</v>
-      </c>
-      <c r="X109">
+        <v>34</v>
+      </c>
+      <c r="P109" t="s">
+        <v>35</v>
+      </c>
+      <c r="W109" t="s">
+        <v>49</v>
+      </c>
+      <c r="X109" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB109">
         <v>10</v>
       </c>
     </row>
@@ -5087,7 +5381,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -5099,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
